--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136347674</v>
       </c>
       <c r="B5" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>136347697</v>
       </c>
       <c r="B13" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136347674</v>
       </c>
       <c r="B5" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>136347697</v>
       </c>
       <c r="B13" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136347674</v>
       </c>
       <c r="B5" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>136347697</v>
       </c>
       <c r="B13" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136347674</v>
       </c>
       <c r="B5" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>136347697</v>
       </c>
       <c r="B13" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136347674</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>136347697</v>
       </c>
       <c r="B13" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43829-2025 artfynd.xlsx
+++ b/artfynd/A 43829-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136347674</v>
       </c>
       <c r="B5" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>136347697</v>
       </c>
       <c r="B13" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
